--- a/artfynd/A 61651-2024 artfynd.xlsx
+++ b/artfynd/A 61651-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126838687</v>
       </c>
       <c r="B2" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126838691</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126838688</v>
       </c>
       <c r="B4" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126838693</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126838690</v>
       </c>
       <c r="B6" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61651-2024 artfynd.xlsx
+++ b/artfynd/A 61651-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126838687</v>
       </c>
       <c r="B2" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126838691</v>
       </c>
       <c r="B3" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126838688</v>
       </c>
       <c r="B4" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126838693</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126838690</v>
       </c>
       <c r="B6" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61651-2024 artfynd.xlsx
+++ b/artfynd/A 61651-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126838687</v>
       </c>
       <c r="B2" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61651-2024 artfynd.xlsx
+++ b/artfynd/A 61651-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126838687</v>
       </c>
       <c r="B2" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126838691</v>
       </c>
       <c r="B3" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126838688</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126838693</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126838690</v>
       </c>
       <c r="B6" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61651-2024 artfynd.xlsx
+++ b/artfynd/A 61651-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126838687</v>
       </c>
       <c r="B2" t="n">
-        <v>91295</v>
+        <v>91284</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126838691</v>
       </c>
       <c r="B3" t="n">
-        <v>80121</v>
+        <v>80114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126838688</v>
       </c>
       <c r="B4" t="n">
-        <v>80150</v>
+        <v>80143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126838693</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126838690</v>
       </c>
       <c r="B6" t="n">
-        <v>80121</v>
+        <v>80114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 61651-2024 artfynd.xlsx
+++ b/artfynd/A 61651-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126838687</v>
       </c>
       <c r="B2" t="n">
-        <v>91284</v>
+        <v>91295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126838691</v>
       </c>
       <c r="B3" t="n">
-        <v>80114</v>
+        <v>80121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126838688</v>
       </c>
       <c r="B4" t="n">
-        <v>80143</v>
+        <v>80150</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126838693</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126838690</v>
       </c>
       <c r="B6" t="n">
-        <v>80114</v>
+        <v>80121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
